--- a/抽奖配置表.xlsx
+++ b/抽奖配置表.xlsx
@@ -398,13 +398,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:C6"/>
   <cols>
-    <col min="1" max="1" width="46.83203125" customWidth="1"/>
-    <col min="2" max="2" width="70.83203125" customWidth="1"/>
-    <col min="3" max="3" width="8.83203125" customWidth="1"/>
-    <col min="4" max="4" width="8.83203125" customWidth="1"/>
-    <col min="5" max="5" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="44.83203125" customWidth="1"/>
+    <col min="2" max="2" width="60.83203125" customWidth="1"/>
+    <col min="3" max="3" width="10.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -420,42 +418,52 @@
         <v>奖品</v>
       </c>
       <c r="C3" t="str">
-        <v>概率1</v>
-      </c>
-      <c r="D3" t="str">
-        <v>概率2</v>
-      </c>
-      <c r="E3" t="str">
-        <v>概率3</v>
+        <v>概率</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>#示例（去掉行首的 # 并改成你的奖品即生效）：抽奖</v>
+        <v>#示例（去掉行首 # 即生效）：抽奖</v>
       </c>
       <c r="B4" t="str">
-        <v>🎉 恭喜抽中一等奖：奶茶一杯！/🎁 恭喜抽中二等奖：贴纸一张/🤏 谢谢参与，下次一定</v>
+        <v>🎉 恭喜抽中一等奖：奶茶一杯！</v>
       </c>
       <c r="C4">
         <v>5</v>
       </c>
-      <c r="D4">
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>#示例：抽奖</v>
+      </c>
+      <c r="B5" t="str">
+        <v>🎁 恭喜抽中二等奖：贴纸一张</v>
+      </c>
+      <c r="C5">
         <v>15</v>
       </c>
-      <c r="E4" t="str">
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>#示例：抽奖</v>
+      </c>
+      <c r="B6" t="str">
+        <v>🤏 谢谢参与，下次一定</v>
+      </c>
+      <c r="C6" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C6"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A14"/>
+  <dimension ref="A1:A11"/>
   <cols>
     <col min="1" max="1" width="110.83203125" customWidth="1"/>
   </cols>
@@ -472,67 +480,52 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>0. 当前示例行以 # 开头（注释行，不生效）——去掉行首 # 并改成你的触发词/奖品/概率即可开启抽奖。</v>
+        <v>0. 玩法：群里 @机器人 发「/触发词」即抽一次（如 /抽奖），机器人按概率抽一条奖品文字原文回复。抽奖是指令，不会误伤普通聊天。</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>1. 一行 = 一个抽奖触发。「触发词」列填触发词，同义词用逗号/顿号/分号分隔放同一格，任一命中即抽一次。</v>
+        <v>1. 一行 = 一个奖品；同一个「触发词」写多行 = 同一个奖池（内容多就多排几行，Excel 下拉填充触发词即可）。</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2. 群消息文字【包含】触发词即命中（不分大小写），无需@机器人，全部群生效；@机器人时也命中且优先于两张回答表。</v>
+        <v>2. 「触发词」格内可用逗号/顿号/分号分隔多个别名（如：抽奖,来一发），任一别名都能触发同一奖池；别名即指令名，别带空格。</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>3. 「奖品」列用 / 分隔多个候选奖品，触发时按概率随机抽一条，抽中的文字【原文】回复到群里（可自带表情和祝贺语）。候选内不要再写 /。</v>
+        <v>3. 「奖品」列填奖品文字，抽中后【原文】回复到群里（可自带表情和祝贺语）；一格一个奖品，不用 / 分隔。</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>4. 「概率1/2/3…」列（奖品列右侧顺延）依次对应第 1/2/3… 个候选奖品，填 0-100 的整数：</v>
+        <v>4. 「概率」列 = 相对权重份数：填 0-100 的数（如 5 和 95 → 5% / 95%）；留空 = 1（等概率参与）；0 = 永不抽中；总和不必凑满 100（自动归一化）。</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v xml:space="preserve">   • 留空的候选自动均分剩余概率（示例：5 + 15 + 留空 → 谢谢参与自动得 80）；</v>
+        <v>5. 触发词以 # 开头的行视为注释行，不同步；触发词/奖品缺一则该行跳过。</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v xml:space="preserve">   • 全部留空 = 等概率；总和不必凑满 100（自动归一化，如 1 和 2 → 33.3%/66.7%）；</v>
+        <v>6. 改完表格 npm run push 同步部署（服务无需重启，配置每条消息实时重读）；本地调试可先跑 npm run sync:lottery。</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v xml:space="preserve">   • 总和超过 100 = 按比例压缩；填 0 = 该奖品永不抽中。</v>
+        <v>7. 群里 @机器人 发 /lottery 可查看当前奖池与各奖品概率；抽奖指令会自动出现在 /help 帮助里。</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>5. 触发词以 # 开头的行视为注释行，不同步；触发词/奖品缺一则该行跳过。</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>6. 改完表格 npm run push 同步部署（服务无需重启，配置每条消息实时重读）；本地调试可先跑 npm run sync:lottery。</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>7. 命中优先级：抽奖触发词 &gt; 「@触发回答」表 &gt; 「关键词回答」表；同一条消息命中多条抽奖规则时逐条各抽一条合并回复。</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>8. 临时启停：运维台定制中心「启停抽奖」，或 POST /api/lottery/enabled（X-API-Token）；查看奖池发 /lottery。</v>
+        <v>8. 临时启停：运维台定制中心「启停抽奖」，或 POST /api/lottery/enabled（X-API-Token）。</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A14"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:A11"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/抽奖配置表.xlsx
+++ b/抽奖配置表.xlsx
@@ -398,72 +398,59 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:B6"/>
   <cols>
-    <col min="1" max="1" width="44.83203125" customWidth="1"/>
-    <col min="2" max="2" width="60.83203125" customWidth="1"/>
-    <col min="3" max="3" width="10.83203125" customWidth="1"/>
+    <col min="1" max="1" width="62.83203125" customWidth="1"/>
+    <col min="2" max="2" width="10.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>抽奖配置表（改完 npm run push 同步部署；详细规则见「使用说明」工作表）</v>
+        <v>抽奖奖池（群里 @机器人 发 /抽奖 即抽一条；改完 npm run push 同步部署；规则见「使用说明」）</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>触发词</v>
+        <v>奖品</v>
       </c>
       <c r="B3" t="str">
-        <v>奖品</v>
-      </c>
-      <c r="C3" t="str">
         <v>概率</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>#示例（去掉行首 # 即生效）：抽奖</v>
-      </c>
-      <c r="B4" t="str">
-        <v>🎉 恭喜抽中一等奖：奶茶一杯！</v>
-      </c>
-      <c r="C4">
+        <v>#示例（去掉行首 # 即生效）：🎉 恭喜抽中一等奖：奶茶一杯！</v>
+      </c>
+      <c r="B4">
         <v>5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>#示例：抽奖</v>
-      </c>
-      <c r="B5" t="str">
-        <v>🎁 恭喜抽中二等奖：贴纸一张</v>
-      </c>
-      <c r="C5">
+        <v>#示例：🎁 恭喜抽中二等奖：贴纸一张</v>
+      </c>
+      <c r="B5">
         <v>15</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>#示例：抽奖</v>
+        <v>#示例：🤏 谢谢参与，下次一定</v>
       </c>
       <c r="B6" t="str">
-        <v>🤏 谢谢参与，下次一定</v>
-      </c>
-      <c r="C6" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B6"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A10"/>
   <cols>
     <col min="1" max="1" width="110.83203125" customWidth="1"/>
   </cols>
@@ -480,32 +467,32 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>0. 玩法：群里 @机器人 发「/触发词」即抽一次（如 /抽奖），机器人按概率抽一条奖品文字原文回复。抽奖是指令，不会误伤普通聊天。</v>
+        <v>0. 玩法：群里 @机器人 发「/抽奖」即抽一次，机器人按概率随机抽一条奖品文字原文回复（中奖哪行回哪行）。</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>1. 一行 = 一个奖品；同一个「触发词」写多行 = 同一个奖池（内容多就多排几行，Excel 下拉填充触发词即可）。</v>
+        <v>1. 整张表就是 /抽奖 的一个大奖池：一行 = 一个奖品，行数不限，想加奖品就往下加行。</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2. 「触发词」格内可用逗号/顿号/分号分隔多个别名（如：抽奖,来一发），任一别名都能触发同一奖池；别名即指令名，别带空格。</v>
+        <v>2. 「奖品」列填奖品文字，可自带表情和祝贺语；以 # 开头的行 = 注释行，不同步。</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>3. 「奖品」列填奖品文字，抽中后【原文】回复到群里（可自带表情和祝贺语）；一格一个奖品，不用 / 分隔。</v>
+        <v>3. 「概率」列 = 相对权重份数：填 0-100 的数（如 5 和 95 → 5% / 95%）；留空 = 1（等概率参与）；0 = 该奖品永不抽中；总和不必凑满 100（自动归一化）。</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>4. 「概率」列 = 相对权重份数：填 0-100 的数（如 5 和 95 → 5% / 95%）；留空 = 1（等概率参与）；0 = 永不抽中；总和不必凑满 100（自动归一化）。</v>
+        <v>4. 指令名默认「抽奖」（/抽奖），可在 server/.env 的 LOTTERY_COMMAND 改名（逗号分隔可配多个别名，如：抽奖,来一发；改完 npm run push 生效）。</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>5. 触发词以 # 开头的行视为注释行，不同步；触发词/奖品缺一则该行跳过。</v>
+        <v>5. 群里 @机器人 发 /lottery 可查看当前奖池与各奖品概率；抽奖指令会自动出现在 /help 帮助里。</v>
       </c>
     </row>
     <row r="9">
@@ -515,17 +502,12 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>7. 群里 @机器人 发 /lottery 可查看当前奖池与各奖品概率；抽奖指令会自动出现在 /help 帮助里。</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>8. 临时启停：运维台定制中心「启停抽奖」，或 POST /api/lottery/enabled（X-API-Token）。</v>
+        <v>7. 临时启停：运维台定制中心「启停抽奖」，或 POST /api/lottery/enabled（X-API-Token）。</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:A10"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/抽奖配置表.xlsx
+++ b/抽奖配置表.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="抽奖配置" sheetId="1" r:id="rId1"/>
+    <sheet name="抽奖" sheetId="1" r:id="rId1"/>
     <sheet name="使用说明" sheetId="2" r:id="rId2"/>
   </sheets>
 </workbook>
@@ -406,7 +406,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>抽奖奖池（群里 @机器人 发 /抽奖 即抽一条；改完 npm run push 同步部署；规则见「使用说明」）</v>
+        <v>/抽奖 奖池（群里 @机器人 发 /抽奖 即抽一条；改完 npm run push 同步部署）</v>
       </c>
     </row>
     <row r="3">
@@ -450,14 +450,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A13"/>
   <cols>
     <col min="1" max="1" width="110.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>「抽奖配置」工作表填写说明</v>
+        <v>抽奖配置表 · 使用说明（一个工作表 = 一个抽奖指令 = 一个奖池）</v>
       </c>
     </row>
     <row r="2">
@@ -467,47 +467,62 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>0. 玩法：群里 @机器人 发「/抽奖」即抽一次，机器人按概率随机抽一条奖品文字原文回复（中奖哪行回哪行）。</v>
+        <v>0. 本表每个工作表对应一个独立的抽奖指令，工作表的名字就是指令名：</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>1. 整张表就是 /抽奖 的一个大奖池：一行 = 一个奖品，行数不限，想加奖品就往下加行。</v>
+        <v xml:space="preserve">   • 工作表「抽奖」→ 群里 @机器人 发 /抽奖；想加第二个抽奖，复制一份工作表、改名（如「转发抽奖」）→ /转发抽奖。</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2. 「奖品」列填奖品文字，可自带表情和祝贺语；以 # 开头的行 = 注释行，不同步。</v>
+        <v xml:space="preserve">   • 本「使用说明」表没有「奖品」表头，自动忽略，随便改；其它没有「奖品」表头的工作表也同样忽略。</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>3. 「概率」列 = 相对权重份数：填 0-100 的数（如 5 和 95 → 5% / 95%）；留空 = 1（等概率参与）；0 = 该奖品永不抽中；总和不必凑满 100（自动归一化）。</v>
+        <v>1. 玩法：群里 @机器人 发「/指令名」即抽一次，机器人按概率随机抽一条奖品文字原文回复（中奖哪行回哪行）。</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>4. 指令名默认「抽奖」（/抽奖），可在 server/.env 的 LOTTERY_COMMAND 改名（逗号分隔可配多个别名，如：抽奖,来一发；改完 npm run push 生效）。</v>
+        <v>2. 奖池表只有「奖品 | 概率」两列：一行 = 一个奖品，行数不限，往下加行即可。</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>5. 群里 @机器人 发 /lottery 可查看当前奖池与各奖品概率；抽奖指令会自动出现在 /help 帮助里。</v>
+        <v>3. 「奖品」列填奖品文字，可自带表情和祝贺语；以 # 开头的行 = 注释行，不同步。</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>6. 改完表格 npm run push 同步部署（服务无需重启，配置每条消息实时重读）；本地调试可先跑 npm run sync:lottery。</v>
+        <v>4. 「概率」列 = 相对权重份数：填 0-100 的数（如 5 和 95 → 5% / 95%）；留空 = 1（等概率参与）；0 = 该奖品永不抽中；总和不必凑满 100（自动归一化）。</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>7. 临时启停：运维台定制中心「启停抽奖」，或 POST /api/lottery/enabled（X-API-Token）。</v>
+        <v>5. 工作表没有有效奖品行时，该指令暂不生效（/指令名 会提示未知指令）；填上奖品再 push 即生效。</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>6. 群里 @机器人 发 /lottery 可查看全部奖池与概率；抽奖指令会自动出现在 /help 帮助里。</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>7. 改完表格 npm run push 同步部署（服务无需重启，配置每条消息实时重读）；本地调试可先跑 npm run sync:lottery。</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>8. 临时启停：运维台定制中心「启停抽奖」，或 POST /api/lottery/enabled（X-API-Token）。</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A10"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:A13"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/抽奖配置表.xlsx
+++ b/抽奖配置表.xlsx
@@ -1,48 +1,175 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\0d00\Desktop\qianli\ticket-pm\project-management-robot\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C33EC733-5186-4823-9C53-DD56BC8257B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-22965" yWindow="10275" windowWidth="19200" windowHeight="11175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet name="抽奖" sheetId="1" r:id="rId1"/>
+    <sheet name="娱乐抽奖" sheetId="1" r:id="rId1"/>
     <sheet name="使用说明" sheetId="2" r:id="rId2"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+  <si>
+    <t>/抽奖 奖池（群里 @机器人 发 /抽奖 即抽一条；改完 npm run push 同步部署）</t>
+  </si>
+  <si>
+    <t>奖品</t>
+  </si>
+  <si>
+    <t>概率</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>抽奖配置表 · 使用说明（一个工作表 = 一个抽奖指令 = 一个奖池）</t>
+  </si>
+  <si>
+    <t>0. 本表每个工作表对应一个独立的抽奖指令，工作表的名字就是指令名：</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   • 工作表「抽奖」→ 群里 @机器人 发 /抽奖；想加第二个抽奖，复制一份工作表、改名（如「转发抽奖」）→ /转发抽奖。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   • 本「使用说明」表没有「奖品」表头，自动忽略，随便改；其它没有「奖品」表头的工作表也同样忽略。</t>
+  </si>
+  <si>
+    <t>1. 玩法：群里 @机器人 发「/指令名」即抽一次，机器人按概率随机抽一条奖品文字原文回复（中奖哪行回哪行）。</t>
+  </si>
+  <si>
+    <t>2. 奖池表只有「奖品 | 概率」两列：一行 = 一个奖品，行数不限，往下加行即可。</t>
+  </si>
+  <si>
+    <t>3. 「奖品」列填奖品文字，可自带表情和祝贺语；以 # 开头的行 = 注释行，不同步。</t>
+  </si>
+  <si>
+    <t>4. 「概率」列 = 相对权重份数：填 0-100 的数（如 5 和 95 → 5% / 95%）；留空 = 1（等概率参与）；0 = 该奖品永不抽中；总和不必凑满 100（自动归一化）。</t>
+  </si>
+  <si>
+    <t>5. 工作表没有有效奖品行时，该指令暂不生效（/指令名 会提示未知指令）；填上奖品再 push 即生效。</t>
+  </si>
+  <si>
+    <t>6. 群里 @机器人 发 /lottery 可查看全部奖池与概率；抽奖指令会自动出现在 /help 帮助里。</t>
+  </si>
+  <si>
+    <t>7. 改完表格 npm run push 同步部署（服务无需重启，配置每条消息实时重读）；本地调试可先跑 npm run sync:lottery。</t>
+  </si>
+  <si>
+    <t>8. 临时启停：运维台定制中心「启停抽奖」，或 POST /api/lottery/enabled（X-API-Token）。</t>
+  </si>
+  <si>
+    <t>666这串腿魔了，你被踢了一脚。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>恭喜你抽到了16.5m/s的大弹丸一发，好痛！</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>恭喜你抽到了爆米花一粒，嘎嘣脆，玉米味。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>恭喜你抽到了爆米花一碗，囔囔囔囔囔囔</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>恭喜你抽到了爆米花一mol，再吃要成大卫带了</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>恭喜你抽到了大石头一块，想要近看还是远看？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>boom！爆米花机爆炸了！你被炸飞了出去</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>恭喜你抽到了20个2006电机，但是都是坏的！</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>怎么还在抽奖，你因为摸鱼被爆米花机拎起来打了一顿</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>恭喜你抽到了一只</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>🐖🐖</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>恭喜你抽到了隐藏奖品。奖励你可以再抽一次！</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>恭喜你抽到了喵板一块，喵喵喵。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>恭喜你抽到了滚木，滚木滚木滚木滚木滚木滚木滚木滚木滚木滚木滚木滚木滚木滚木滚木滚木滚木滚木滚木滚木滚木滚木滚木滚木</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>恭喜你抽到了隐藏奖品。奖励你必须立刻造7台串腿！</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>恭喜你抽到了大狗，大狗不想叫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>恭喜你抽到了大狗，大狗把你嚼嚼嚼了（悲）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Segoe UI Symbol"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -66,13 +193,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -397,132 +532,242 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B19"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="62.83203125" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>/抽奖 奖池（群里 @机器人 发 /抽奖 即抽一条；改完 npm run push 同步部署）</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>奖品</v>
-      </c>
-      <c r="B3" t="str">
-        <v>概率</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>#示例（去掉行首 # 即生效）：🎉 恭喜抽中一等奖：奶茶一杯！</v>
+    <row r="1" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>16</v>
       </c>
       <c r="B4">
         <v>5</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>#示例：🎁 恭喜抽中二等奖：贴纸一张</v>
+    <row r="5" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>17</v>
       </c>
       <c r="B5">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>#示例：🤏 谢谢参与，下次一定</v>
-      </c>
-      <c r="B6" t="str">
-        <v/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="17.5" x14ac:dyDescent="0.45">
+      <c r="A13" t="s">
+        <v>25</v>
+      </c>
+      <c r="B13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="17.5" x14ac:dyDescent="0.45">
+      <c r="A14" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>27</v>
+      </c>
+      <c r="B16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>28</v>
+      </c>
+      <c r="B17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>30</v>
+      </c>
+      <c r="B18">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>31</v>
+      </c>
+      <c r="B19">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B6"/>
+    <ignoredError sqref="A1:B3 B4" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:A13"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="110.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>抽奖配置表 · 使用说明（一个工作表 = 一个抽奖指令 = 一个奖池）</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>0. 本表每个工作表对应一个独立的抽奖指令，工作表的名字就是指令名：</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v xml:space="preserve">   • 工作表「抽奖」→ 群里 @机器人 发 /抽奖；想加第二个抽奖，复制一份工作表、改名（如「转发抽奖」）→ /转发抽奖。</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v xml:space="preserve">   • 本「使用说明」表没有「奖品」表头，自动忽略，随便改；其它没有「奖品」表头的工作表也同样忽略。</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>1. 玩法：群里 @机器人 发「/指令名」即抽一次，机器人按概率随机抽一条奖品文字原文回复（中奖哪行回哪行）。</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>2. 奖池表只有「奖品 | 概率」两列：一行 = 一个奖品，行数不限，往下加行即可。</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>3. 「奖品」列填奖品文字，可自带表情和祝贺语；以 # 开头的行 = 注释行，不同步。</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>4. 「概率」列 = 相对权重份数：填 0-100 的数（如 5 和 95 → 5% / 95%）；留空 = 1（等概率参与）；0 = 该奖品永不抽中；总和不必凑满 100（自动归一化）。</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>5. 工作表没有有效奖品行时，该指令暂不生效（/指令名 会提示未知指令）；填上奖品再 push 即生效。</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>6. 群里 @机器人 发 /lottery 可查看全部奖池与概率；抽奖指令会自动出现在 /help 帮助里。</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>7. 改完表格 npm run push 同步部署（服务无需重启，配置每条消息实时重读）；本地调试可先跑 npm run sync:lottery。</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>8. 临时启停：运维台定制中心「启停抽奖」，或 POST /api/lottery/enabled（X-API-Token）。</v>
+    <row r="1" spans="1:1" ht="15" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" ht="15" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" ht="15" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" ht="15" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" ht="15" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" ht="15" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" ht="15" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" ht="15" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" ht="15" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" ht="15" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" ht="15" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" ht="15" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" ht="15" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A13"/>
+    <ignoredError sqref="A1:A13" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/抽奖配置表.xlsx
+++ b/抽奖配置表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\0d00\Desktop\qianli\ticket-pm\project-management-robot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C33EC733-5186-4823-9C53-DD56BC8257B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6E49D2F-C1DF-4AF8-95CC-B5D1123706FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-22965" yWindow="10275" windowWidth="19200" windowHeight="11175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
   <si>
     <t>/抽奖 奖池（群里 @机器人 发 /抽奖 即抽一条；改完 npm run push 同步部署）</t>
   </si>
@@ -145,12 +145,69 @@
     <t>恭喜你抽到了大狗，大狗把你嚼嚼嚼了（悲）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>你抽到了3D打印耗材1g，联系曼波领取打印额度</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>你抽奖的动静打扰了了一位忍者。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>🥷</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>：吓我一跳我释放忍术。你被打败了</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>你抽到了3D打印耗材1t，你被耗材压扁了</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>恭喜你抽到了毛绒小蜥蜴一只，啊——</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>恭喜你抽到了dji胡萝贝一只，胡萝贝要去当操作手了</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>恭喜你抽到了好果汁，喝完就去干活</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>恭喜你抽到了维拉M12扳手一根，拿去修理电控吧！</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>恭喜你抽到了WD40一瓶，这个我从小喝到大。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>恭喜你抽到了烧了的满电tb48s一块，千里小伙能量大，一动不动就爆炸。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -169,6 +226,19 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Segoe UI Symbol"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Segoe UI Emoji"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -533,19 +603,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B19"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:B28"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="62.83203125" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -553,7 +623,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -561,7 +631,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -569,7 +639,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -633,7 +703,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="17.5" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>26</v>
       </c>
@@ -654,7 +724,7 @@
         <v>27</v>
       </c>
       <c r="B16">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -679,6 +749,78 @@
       </c>
       <c r="B19">
         <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>32</v>
+      </c>
+      <c r="B20">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="17.5" x14ac:dyDescent="0.45">
+      <c r="A21" t="s">
+        <v>33</v>
+      </c>
+      <c r="B21">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>34</v>
+      </c>
+      <c r="B22">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>35</v>
+      </c>
+      <c r="B23">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>36</v>
+      </c>
+      <c r="B24">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>37</v>
+      </c>
+      <c r="B25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>40</v>
+      </c>
+      <c r="B26">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>38</v>
+      </c>
+      <c r="B27">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>39</v>
+      </c>
+      <c r="B28">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -693,72 +835,72 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:A13"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="110.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:1" ht="15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:1" ht="15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:1" ht="15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:1" ht="15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:1" ht="15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:1" ht="15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:1" ht="15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:1" ht="15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:1" ht="15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:1" ht="15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:1" ht="15" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>15</v>
       </c>

--- a/抽奖配置表.xlsx
+++ b/抽奖配置表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\0d00\Desktop\qianli\ticket-pm\project-management-robot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6E49D2F-C1DF-4AF8-95CC-B5D1123706FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6981FE12-E9C8-4EEA-8E05-87C753C30941}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-22965" yWindow="10275" windowWidth="19200" windowHeight="11175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
   <si>
     <t>/抽奖 奖池（群里 @机器人 发 /抽奖 即抽一条；改完 npm run push 同步部署）</t>
   </si>
@@ -200,6 +200,44 @@
   </si>
   <si>
     <t>恭喜你抽到了烧了的满电tb48s一块，千里小伙能量大，一动不动就爆炸。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>恭喜你抽到了毛绒料理鼠王一只，已开启自动驾驶模式</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>恭喜你抽到了</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>🍞</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>🍞🍞🍞</t>
+    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -603,7 +641,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B28"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="62.83203125" customWidth="1"/>
@@ -820,6 +858,22 @@
         <v>39</v>
       </c>
       <c r="B28">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>41</v>
+      </c>
+      <c r="B29">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" ht="17.5" x14ac:dyDescent="0.45">
+      <c r="A31" t="s">
+        <v>42</v>
+      </c>
+      <c r="B31">
         <v>3</v>
       </c>
     </row>

--- a/抽奖配置表.xlsx
+++ b/抽奖配置表.xlsx
@@ -8,20 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\0d00\Desktop\qianli\ticket-pm\project-management-robot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6981FE12-E9C8-4EEA-8E05-87C753C30941}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D2E8AF3-8861-483B-A216-C75F8522AFD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-22965" yWindow="10275" windowWidth="19200" windowHeight="11175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="28800" windowHeight="15225" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="娱乐抽奖" sheetId="1" r:id="rId1"/>
     <sheet name="使用说明" sheetId="2" r:id="rId2"/>
+    <sheet name="严肃抽奖" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="45">
   <si>
     <t>/抽奖 奖池（群里 @机器人 发 /抽奖 即抽一条；改完 npm run push 同步部署）</t>
   </si>
@@ -238,6 +239,14 @@
       </rPr>
       <t>🍞🍞🍞</t>
     </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>恭喜你抽到了</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>恭喜你抽到了22米吊射命中100%的重装机器人</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -642,18 +651,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B31"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="62.83203125" customWidth="1"/>
-    <col min="2" max="2" width="10.83203125" customWidth="1"/>
+    <col min="1" max="1" width="62.875" customWidth="1"/>
+    <col min="2" max="2" width="10.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -661,7 +670,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -669,7 +678,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -677,7 +686,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -685,7 +694,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A7" t="s">
         <v>19</v>
       </c>
@@ -693,7 +702,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A8" t="s">
         <v>20</v>
       </c>
@@ -701,7 +710,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A9" t="s">
         <v>21</v>
       </c>
@@ -709,7 +718,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A10" t="s">
         <v>22</v>
       </c>
@@ -717,7 +726,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A11" t="s">
         <v>23</v>
       </c>
@@ -725,7 +734,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A12" t="s">
         <v>24</v>
       </c>
@@ -733,7 +742,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="17.5" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:2" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>25</v>
       </c>
@@ -741,7 +750,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A14" t="s">
         <v>26</v>
       </c>
@@ -749,7 +758,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A15" t="s">
         <v>29</v>
       </c>
@@ -757,7 +766,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A16" t="s">
         <v>27</v>
       </c>
@@ -765,7 +774,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A17" t="s">
         <v>28</v>
       </c>
@@ -773,7 +782,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A18" t="s">
         <v>30</v>
       </c>
@@ -781,7 +790,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A19" t="s">
         <v>31</v>
       </c>
@@ -789,7 +798,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A20" t="s">
         <v>32</v>
       </c>
@@ -797,7 +806,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="17.5" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:2" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>33</v>
       </c>
@@ -805,7 +814,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A22" t="s">
         <v>34</v>
       </c>
@@ -813,7 +822,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A23" t="s">
         <v>35</v>
       </c>
@@ -821,7 +830,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A24" t="s">
         <v>36</v>
       </c>
@@ -829,7 +838,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A25" t="s">
         <v>37</v>
       </c>
@@ -837,7 +846,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A26" t="s">
         <v>40</v>
       </c>
@@ -845,7 +854,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A27" t="s">
         <v>38</v>
       </c>
@@ -853,7 +862,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A28" t="s">
         <v>39</v>
       </c>
@@ -861,7 +870,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A29" t="s">
         <v>41</v>
       </c>
@@ -869,7 +878,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="31" spans="1:2" ht="17.5" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:2" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>42</v>
       </c>
@@ -889,72 +898,72 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:A13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="110.83203125" customWidth="1"/>
+    <col min="1" max="1" width="110.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A6" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A7" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A8" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A9" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A10" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A11" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A12" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A13" t="s">
         <v>15</v>
       </c>
@@ -966,4 +975,40 @@
     <ignoredError sqref="A1:A13" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2D65CF0-5BE9-46CC-82EE-FCC2EDCE5B30}">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="1" max="1" width="85.625" customWidth="1"/>
+    <col min="2" max="2" width="42.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/抽奖配置表.xlsx
+++ b/抽奖配置表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\0d00\Desktop\qianli\ticket-pm\project-management-robot\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D2E8AF3-8861-483B-A216-C75F8522AFD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62728CAD-0661-4022-8AA1-2BAE3BFAAE85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="28800" windowHeight="15225" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="28800" windowHeight="15345" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="娱乐抽奖" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="62">
   <si>
     <t>/抽奖 奖池（群里 @机器人 发 /抽奖 即抽一条；改完 npm run push 同步部署）</t>
   </si>
@@ -242,11 +242,79 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>恭喜你抽到了</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>恭喜你抽到了22米吊射命中100%的重装机器人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>恭喜你抽到了12米散步一个点的步兵发射</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>恭喜你抽到了10巴掌</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>恭喜你抽到了100巴掌</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>恭喜你抽到了67巴掌</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>恭喜你抽到了514巴掌</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>恭喜你抽到了1919810巴掌</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>恭喜你抽到了迷路的哨兵</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>恭喜你抽到了末端移动4中4的飞镖机器人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>恭喜你抽到了随机移动4中3的飞镖机器人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>恭喜你抽到了固定靶4中4的飞镖机器人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>恭喜你抽到了固定靶4中0的飞镖机器人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>恭喜你抽到了本轮mvp兵种：重装</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>恭喜你抽到了本轮mvp兵种：步兵</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>恭喜你抽到了本轮mvp兵种：哨兵</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>恭喜你抽到了本轮mvp兵种：飞镖</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>恭喜你抽到了本轮mvp兵种：空中</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>恭喜你抽到了本轮mvp兵种：雷达</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>恭喜你抽到了内置gpt6 ultra的哨兵机器人</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -979,7 +1047,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2D65CF0-5BE9-46CC-82EE-FCC2EDCE5B30}">
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="85.625" customWidth="1"/>
@@ -996,7 +1064,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B2">
         <v>3</v>
@@ -1004,7 +1072,146 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="B3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A7" t="s">
+        <v>48</v>
+      </c>
+      <c r="B7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A8" t="s">
+        <v>49</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A9" t="s">
+        <v>50</v>
+      </c>
+      <c r="B9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A10" t="s">
+        <v>51</v>
+      </c>
+      <c r="B10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A11" t="s">
+        <v>52</v>
+      </c>
+      <c r="B11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A12" t="s">
+        <v>53</v>
+      </c>
+      <c r="B12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A13" t="s">
+        <v>54</v>
+      </c>
+      <c r="B13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A14" t="s">
+        <v>55</v>
+      </c>
+      <c r="B14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A15" t="s">
+        <v>56</v>
+      </c>
+      <c r="B15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A16" t="s">
+        <v>57</v>
+      </c>
+      <c r="B16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A17" t="s">
+        <v>59</v>
+      </c>
+      <c r="B17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A18" t="s">
+        <v>58</v>
+      </c>
+      <c r="B18">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A19" t="s">
+        <v>60</v>
+      </c>
+      <c r="B19">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.15">
+      <c r="A20" t="s">
+        <v>61</v>
+      </c>
+      <c r="B20">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
